--- a/data/tpl-人工造林-验收流程模板.xlsx
+++ b/data/tpl-人工造林-验收流程模板.xlsx
@@ -31,7 +31,7 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="5">'流程-完工验收'!$1:$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'流程-日常巡护'!$A$1:$F$4</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="6">'流程-日常巡护'!$1:$1</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="7">'说明'!$A$1:$F$70</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="7">'说明'!$A$1:$F$78</definedName>
   </definedNames>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
@@ -40,7 +40,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="37">
+  <fonts count="40">
     <font>
       <name val="宋体"/>
       <charset val="134"/>
@@ -300,8 +300,25 @@
       <color rgb="00000000"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="PingFang SC"/>
+      <b val="1"/>
+      <color rgb="00375623"/>
+      <sz val="16"/>
+    </font>
+    <font>
+      <name val="PingFang SC"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="PingFang SC"/>
+      <color rgb="00000000"/>
+      <sz val="9"/>
+    </font>
   </fonts>
-  <fills count="41">
+  <fills count="43">
     <fill>
       <patternFill/>
     </fill>
@@ -541,8 +558,18 @@
         <fgColor rgb="007F6000"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00375623"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001F4E78"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="16">
+  <borders count="19">
     <border>
       <left/>
       <right/>
@@ -739,6 +766,39 @@
         <color rgb="00BFBFBF"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00BFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00BFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0"/>
@@ -887,7 +947,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -974,6 +1034,43 @@
     <xf numFmtId="0" fontId="36" fillId="0" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="41" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="42" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -13886,13 +13983,13 @@
       </c>
       <c r="D7" s="10" t="inlineStr">
         <is>
-          <t>数值(株)</t>
+          <t>数值(株→≥设计值)</t>
         </is>
       </c>
       <c r="E7" s="10" t="n"/>
       <c r="F7" s="12" t="inlineStr">
         <is>
-          <t>原表头：核实总数量（按实际测量填写）；按数值填写，与设计值自动对照。</t>
+          <t>原表头：核实总数量（按实际测量填写）；按数值填写，与设计值自动对照。 通过判断：≥设计值</t>
         </is>
       </c>
     </row>
@@ -14040,13 +14137,13 @@
       </c>
       <c r="D3" s="11" t="inlineStr">
         <is>
-          <t>选项(正确;未实施施肥;未达到每株1.5kg)</t>
+          <t>选项(正确;未实施施肥→备注≥2;未达到每株1.5kg→备注≥2)</t>
         </is>
       </c>
       <c r="E3" s="10" t="n"/>
       <c r="F3" s="12" t="inlineStr">
         <is>
-          <t>原表头：有机肥1.5kg/株(1.已实施施肥2.未实施施肥3.达到每株1.5kg4.未达到每株1.5kg )；「正确」在首位，其余为错误项，选中即记录。</t>
+          <t>原表头：有机肥1.5kg/株(1.已实施施肥2.未实施施肥3.达到每株1.5kg4.未达到每株1.5kg )；「正确」在首位，其余为错误项，选中后须在本环节填 ≥2 汉字备注。</t>
         </is>
       </c>
     </row>
@@ -14066,13 +14163,13 @@
       </c>
       <c r="D4" s="11" t="inlineStr">
         <is>
-          <t>选项(正确;未实施施肥;未达到每株0.2kg)</t>
+          <t>选项(正确;未实施施肥→备注≥2;未达到每株0.2kg→备注≥2)</t>
         </is>
       </c>
       <c r="E4" s="10" t="n"/>
       <c r="F4" s="12" t="inlineStr">
         <is>
-          <t>原表头：普钙0.2kg/株(1.已实施施肥2.未实施施肥3.达到每株0.2kg4.未达到每株0.2kg )；「正确」在首位，其余为错误项，选中即记录。</t>
+          <t>原表头：普钙0.2kg/株(1.已实施施肥2.未实施施肥3.达到每株0.2kg4.未达到每株0.2kg )；「正确」在首位，其余为错误项，选中后须在本环节填 ≥2 汉字备注。</t>
         </is>
       </c>
     </row>
@@ -14324,13 +14421,13 @@
       </c>
       <c r="D6" s="10" t="inlineStr">
         <is>
-          <t>数值(株)</t>
+          <t>数值(株→≥设计值)</t>
         </is>
       </c>
       <c r="E6" s="10" t="n"/>
       <c r="F6" s="12" t="inlineStr">
         <is>
-          <t>原表头：核实栽植总株数（1.达标2.不达标（填写实际数量））；按数值填写，与设计值自动对照。</t>
+          <t>原表头：核实栽植总株数（1.达标2.不达标（填写实际数量））；按数值填写，与设计值自动对照。 通过判断：≥设计值</t>
         </is>
       </c>
     </row>
@@ -14350,13 +14447,13 @@
       </c>
       <c r="D7" s="10" t="inlineStr">
         <is>
-          <t>数值(株)</t>
+          <t>数值(株→≥设计值)</t>
         </is>
       </c>
       <c r="E7" s="10" t="n"/>
       <c r="F7" s="12" t="inlineStr">
         <is>
-          <t>源表同名列第 2 次出现，按列位置取「树种1株数（株）」。原表头：核实栽植总株数（1.达标2.不达标（填写实际数量））；按数值填写，与设计值自动对照。</t>
+          <t>源表同名列第 2 次出现，按列位置取「树种1株数（株）」。原表头：核实栽植总株数（1.达标2.不达标（填写实际数量））；按数值填写，与设计值自动对照。 通过判断：≥设计值</t>
         </is>
       </c>
     </row>
@@ -14376,13 +14473,13 @@
       </c>
       <c r="D8" s="10" t="inlineStr">
         <is>
-          <t>数值(株)</t>
+          <t>数值(株→≥设计值)</t>
         </is>
       </c>
       <c r="E8" s="10" t="n"/>
       <c r="F8" s="12" t="inlineStr">
         <is>
-          <t>源表同名列第 3 次出现，按列位置取「树种2株数（株）」。原表头：核实栽植总株数（1.达标2.不达标（填写实际数量））；按数值填写，与设计值自动对照。</t>
+          <t>源表同名列第 3 次出现，按列位置取「树种2株数（株）」。原表头：核实栽植总株数（1.达标2.不达标（填写实际数量））；按数值填写，与设计值自动对照。 通过判断：≥设计值</t>
         </is>
       </c>
     </row>
@@ -14402,13 +14499,13 @@
       </c>
       <c r="D9" s="10" t="inlineStr">
         <is>
-          <t>数值(株)</t>
+          <t>数值(株→≥设计值)</t>
         </is>
       </c>
       <c r="E9" s="10" t="n"/>
       <c r="F9" s="12" t="inlineStr">
         <is>
-          <t>原表头：核实撑杆数量（1.数量达标2.数量不达标（填写实际数量）3.撑杆规格达标4.撑杆规格不达标）；原表把数量与规格合在一列，这里拆成「核实撑杆数量（数值）+ 撑杆规格（选项）」两行。</t>
+          <t>原表头：核实撑杆数量（1.数量达标2.数量不达标（填写实际数量）3.撑杆规格达标4.撑杆规格不达标）；原表把数量与规格合在一列，这里拆成「核实撑杆数量（数值）+ 撑杆规格（选项）」两行。 通过判断：≥设计值</t>
         </is>
       </c>
     </row>
@@ -14454,13 +14551,13 @@
       </c>
       <c r="D11" s="10" t="inlineStr">
         <is>
-          <t>数值(株)</t>
+          <t>数值(株→≥设计值)</t>
         </is>
       </c>
       <c r="E11" s="10" t="n"/>
       <c r="F11" s="12" t="inlineStr">
         <is>
-          <t>原表头：核实覆膜数量（1.数量达标2.数量不达标（填写实际数量）3.覆膜质量达标4.覆膜质量不达标）；原表把数量与质量合在一列，这里拆成「核实覆膜数量（数值）+ 覆膜质量（选项）」两行。</t>
+          <t>原表头：核实覆膜数量（1.数量达标2.数量不达标（填写实际数量）3.覆膜质量达标4.覆膜质量不达标）；原表把数量与质量合在一列，这里拆成「核实覆膜数量（数值）+ 覆膜质量（选项）」两行。 通过判断：≥设计值</t>
         </is>
       </c>
     </row>
@@ -14712,13 +14809,13 @@
       </c>
       <c r="D6" s="10" t="inlineStr">
         <is>
-          <t>数值(株)</t>
+          <t>数值(株→≥设计值)</t>
         </is>
       </c>
       <c r="E6" s="10" t="n"/>
       <c r="F6" s="12" t="inlineStr">
         <is>
-          <t>原表头：核实栽植总株数（1.达标2.不达标（填写实际数量））；按数值填写，与设计值自动对照。</t>
+          <t>原表头：核实栽植总株数（1.达标2.不达标（填写实际数量））；按数值填写，与设计值自动对照。 通过判断：≥设计值</t>
         </is>
       </c>
     </row>
@@ -14738,13 +14835,13 @@
       </c>
       <c r="D7" s="10" t="inlineStr">
         <is>
-          <t>数值(株)</t>
+          <t>数值(株→≥设计值)</t>
         </is>
       </c>
       <c r="E7" s="10" t="n"/>
       <c r="F7" s="12" t="inlineStr">
         <is>
-          <t>源表同名列第 2 次出现，按列位置取「树种1株数（株）」。原表头：核实栽植总株数（1.达标2.不达标（填写实际数量））；按数值填写，与设计值自动对照。</t>
+          <t>源表同名列第 2 次出现，按列位置取「树种1株数（株）」。原表头：核实栽植总株数（1.达标2.不达标（填写实际数量））；按数值填写，与设计值自动对照。 通过判断：≥设计值</t>
         </is>
       </c>
     </row>
@@ -14764,13 +14861,13 @@
       </c>
       <c r="D8" s="10" t="inlineStr">
         <is>
-          <t>数值(株)</t>
+          <t>数值(株→≥设计值)</t>
         </is>
       </c>
       <c r="E8" s="10" t="n"/>
       <c r="F8" s="12" t="inlineStr">
         <is>
-          <t>源表同名列第 3 次出现，按列位置取「树种2株数（株）」。原表头：核实栽植总株数（1.达标2.不达标（填写实际数量））；按数值填写，与设计值自动对照。</t>
+          <t>源表同名列第 3 次出现，按列位置取「树种2株数（株）」。原表头：核实栽植总株数（1.达标2.不达标（填写实际数量））；按数值填写，与设计值自动对照。 通过判断：≥设计值</t>
         </is>
       </c>
     </row>
@@ -14786,13 +14883,13 @@
       <c r="C9" s="10" t="inlineStr"/>
       <c r="D9" s="10" t="inlineStr">
         <is>
-          <t>百分数(0-100)</t>
+          <t>百分数(0-100→≥85)</t>
         </is>
       </c>
       <c r="E9" s="10" t="n"/>
       <c r="F9" s="12" t="inlineStr">
         <is>
-          <t>原表头：栽植成活率（按实际测算填写）；填 0-100 的百分数。</t>
+          <t>原表头：栽植成活率（按实际测算填写）；填 0-100 的百分数。 通过判断：≥85</t>
         </is>
       </c>
     </row>
@@ -14812,13 +14909,13 @@
       </c>
       <c r="D10" s="10" t="inlineStr">
         <is>
-          <t>数值(株)</t>
+          <t>数值(株→≥设计值)</t>
         </is>
       </c>
       <c r="E10" s="10" t="n"/>
       <c r="F10" s="12" t="inlineStr">
         <is>
-          <t>原表头：核实撑杆数量（1.数量达标2.数量不达标（填写实际数量）3.撑杆规格达标4.撑杆规格不达标）；原表把数量与规格合在一列，这里拆成「核实撑杆数量（数值）+ 撑杆规格（选项）」两行。</t>
+          <t>原表头：核实撑杆数量（1.数量达标2.数量不达标（填写实际数量）3.撑杆规格达标4.撑杆规格不达标）；原表把数量与规格合在一列，这里拆成「核实撑杆数量（数值）+ 撑杆规格（选项）」两行。 通过判断：≥设计值</t>
         </is>
       </c>
     </row>
@@ -14864,13 +14961,13 @@
       </c>
       <c r="D12" s="10" t="inlineStr">
         <is>
-          <t>数值(株)</t>
+          <t>数值(株→≥设计值)</t>
         </is>
       </c>
       <c r="E12" s="10" t="n"/>
       <c r="F12" s="12" t="inlineStr">
         <is>
-          <t>原表头：核实覆膜数量（1.数量达标2.数量不达标（填写实际数量）3.覆膜质量达标4.覆膜质量不达标）；原表把数量与质量合在一列，这里拆成「核实覆膜数量（数值）+ 覆膜质量（选项）」两行。</t>
+          <t>原表头：核实覆膜数量（1.数量达标2.数量不达标（填写实际数量）3.覆膜质量达标4.覆膜质量不达标）；原表把数量与质量合在一列，这里拆成「核实覆膜数量（数值）+ 覆膜质量（选项）」两行。 通过判断：≥设计值</t>
         </is>
       </c>
     </row>
@@ -14956,13 +15053,13 @@
       <c r="C16" s="10" t="inlineStr"/>
       <c r="D16" s="15" t="inlineStr">
         <is>
-          <t>自动(成活株数/(成活株数+死亡株数)×100%)</t>
+          <t>自动(成活株数/(成活株数+死亡株数)×100%→≥85)</t>
         </is>
       </c>
       <c r="E16" s="10" t="n"/>
       <c r="F16" s="12" t="inlineStr">
         <is>
-          <t>原表头：样地调查成活率；自动计算，不手填。</t>
+          <t>原表头：样地调查成活率；自动计算，不手填。 通过判断：≥85</t>
         </is>
       </c>
     </row>
@@ -15083,7 +15180,11 @@
           <t>多选(林地清理、整地巡护;底肥放置、回塘巡护;栽植、撑杆覆膜巡护;其他日常巡护)</t>
         </is>
       </c>
-      <c r="E2" s="10" t="n"/>
+      <c r="E2" s="10" t="inlineStr">
+        <is>
+          <t>上传:巡护资料@3(图片≥1;PDF≥1)</t>
+        </is>
+      </c>
       <c r="F2" s="12" t="inlineStr">
         <is>
           <t>原表头：巡护情况（1，林地清理、整地巡护；2，底肥放置、回塘巡护，3栽植、撑杆覆膜巡护，4， 其他日常巡护）；可多选。</t>
@@ -15145,770 +15246,846 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="FF7F7F7F"/>
+    <tabColor rgb="007F7F7F"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F70"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8"/>
+  <dimension ref="A1:F78"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="2"/>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
     <col width="30" customWidth="1" min="3" max="3"/>
     <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="34" customWidth="1" min="5" max="6"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
+    <col width="34" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="36" t="inlineStr">
         <is>
           <t>tpl-人工造林-验收流程模板 · 说明</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>版本 v2.3 ｜ 2026-10-27 ｜ 来源：tpl- 流程-人工造林.xlsx</t>
+      <c r="A2" s="37" t="inlineStr">
+        <is>
+          <t>版本 v2.7 ｜ 2026-10-28 ｜ 来源：tpl-人工造林-验收流程模板.xlsx</t>
         </is>
       </c>
     </row>
     <row r="3" ht="30" customHeight="1">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="37" t="inlineStr">
         <is>
           <t>口径：模板由 tools/tpl_tool.py 从源表头自动解析生成；新增项目 / 流程只改源表或加 sheet，不改解析代码。</t>
         </is>
       </c>
     </row>
     <row r="5" ht="24" customHeight="1">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="A5" s="38" t="inlineStr">
         <is>
           <t>一、Sheet 约定</t>
         </is>
       </c>
     </row>
     <row r="6" ht="34" customHeight="1">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="39" t="inlineStr">
         <is>
           <t>设计值（第一个 sheet）</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="C6" s="37" t="inlineStr">
         <is>
           <t>一行 = 一个小班。A 列「项目类型」默认「人工造乔木林」；蓝底 = 身份键，绿底 = 设计值。149 个唯一小班，5 个源 sheet 按小班号合并去重。</t>
         </is>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="39" t="inlineStr">
         <is>
           <t>流程路由</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="C7" s="37" t="inlineStr">
         <is>
           <t>一行 = 一条路由。列 = 序号 / 项目类型 / 流程 / 前置流程 / 可重复 / 触发方式 / 说明；决定同一项目类型下各流程的先后、并行与重复。</t>
         </is>
       </c>
     </row>
     <row r="8" ht="30" customHeight="1">
-      <c r="A8" s="4" t="inlineStr">
+      <c r="A8" s="39" t="inlineStr">
         <is>
           <t>流程-*（5 个）</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="C8" s="37" t="inlineStr">
         <is>
           <t>一行 = 一个环节。列 = 序号 / 环节 / 设计值表头 / 控件 / 附件 / 备注。不含填报数据，只是界面定义。</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="30" customHeight="1">
-      <c r="A9" s="4" t="inlineStr">
+    <row r="9" ht="34" customHeight="1">
+      <c r="A9" s="39" t="inlineStr">
+        <is>
+          <t>参数</t>
+        </is>
+      </c>
+      <c r="C9" s="37" t="inlineStr">
+        <is>
+          <t>程序读取的配置（搜索栏顺序、功能、唯一键、导出筛选）。由 tpl_tool.py 的 params 命令同步：程序新增 key 时只补行，已有值不覆盖。</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="30" customHeight="1">
+      <c r="A10" s="39" t="inlineStr">
         <is>
           <t>说明</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="C10" s="37" t="inlineStr">
         <is>
           <t>本页：列语义、控件 DSL、设计值来源、解析约定。</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="24" customHeight="1">
-      <c r="A11" s="3" t="inlineStr">
+    <row r="12" ht="24" customHeight="1">
+      <c r="A12" s="38" t="inlineStr">
         <is>
           <t>二、流程路由</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="24" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
+    <row r="13" ht="24" customHeight="1">
+      <c r="A13" s="37" t="inlineStr">
         <is>
           <t>主线（按序、每步一次）：流程-整地 → 流程-回塘底肥 → 流程-栽植撑杆覆膜 → 流程-完工验收。</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="30" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>独立（序号 0、无前置、可重复）：流程-日常巡护，无前置流程；随时可发起，可多次；不参与主线默认选择，也不阻塞 / 解锁任何前后流程。</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="30" customHeight="1">
-      <c r="A14" s="4" t="inlineStr">
+    <row r="14" ht="34" customHeight="1">
+      <c r="A14" s="37" t="inlineStr">
+        <is>
+          <t>独立（序号 0、无前置、可重复）：流程-日常巡护；随时可发起，可多次，不参与主线默认选择，也不影响任何前后关系。</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="30" customHeight="1">
+      <c r="A15" s="39" t="inlineStr">
         <is>
           <t>项目类型</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
+      <c r="C15" s="37" t="inlineStr">
         <is>
           <t>与「设计值」A 列一致；一个项目类型一套路由，新增类型只需加行。</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="34" customHeight="1">
-      <c r="A15" s="4" t="inlineStr">
+    <row r="16" ht="34" customHeight="1">
+      <c r="A16" s="39" t="inlineStr">
         <is>
           <t>前置流程</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
+      <c r="C16" s="37" t="inlineStr">
         <is>
           <t>可写多个，用 ; 分隔 = 全部完成后才可发起；留空 = 随时可发起；只能引用同项目类型内的流程。</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="34" customHeight="1">
-      <c r="A16" s="4" t="inlineStr">
+    <row r="17" ht="34" customHeight="1">
+      <c r="A17" s="39" t="inlineStr">
         <is>
           <t>可重复 / 触发方式</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
+      <c r="C17" s="37" t="inlineStr">
         <is>
           <t>可重复：是 = 可多次（如巡护），否 = 仅一次（如完工验收）。触发方式：按序 = 前置完成后进入，按需 = 手动发起，定期 = 按周期发起。</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="30" customHeight="1">
-      <c r="A17" s="4" t="inlineStr">
+    <row r="18" ht="30" customHeight="1">
+      <c r="A18" s="39" t="inlineStr">
         <is>
           <t>新增流程</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr">
+      <c r="C18" s="37" t="inlineStr">
         <is>
           <t>源表加 sheet 后重新 build，路由默认串到前一流程之后；再按实际调整前置 / 重复 / 触发。</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="24" customHeight="1">
-      <c r="A19" s="3" t="inlineStr">
+    <row r="20" ht="24" customHeight="1">
+      <c r="A20" s="38" t="inlineStr">
         <is>
           <t>三、流程表 6 列</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="24" customHeight="1">
-      <c r="A20" s="4" t="inlineStr">
+    <row r="21" ht="30" customHeight="1">
+      <c r="A21" s="39" t="inlineStr">
         <is>
           <t>序号</t>
         </is>
       </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>界面顺序；也是流程内唯一编号。</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="30" customHeight="1">
-      <c r="A21" s="4" t="inlineStr">
+      <c r="C21" s="37" t="inlineStr">
+        <is>
+          <t>主线界面顺序（1 起）；**序号 0 = 独立流程**，界面排在主线之后、不参与默认选择。</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="30" customHeight="1">
+      <c r="A22" s="39" t="inlineStr">
         <is>
           <t>环节</t>
         </is>
       </c>
-      <c r="C21" s="2" t="inlineStr">
+      <c r="C22" s="37" t="inlineStr">
         <is>
           <t>本流程中的一个填报 / 核验项，取自源表黑色表头，已去掉括号里的选项说明。</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="34" customHeight="1">
-      <c r="A22" s="4" t="inlineStr">
+    <row r="23" ht="34" customHeight="1">
+      <c r="A23" s="39" t="inlineStr">
         <is>
           <t>设计值表头</t>
         </is>
       </c>
-      <c r="C22" s="2" t="inlineStr">
+      <c r="C23" s="37" t="inlineStr">
         <is>
           <t>写「设计值」sheet 的列名。运行时按当前小班取该列值，自动显示在表单里作提示；「常量：xxx」为固定提示；留空 = 无设计值。</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="24" customHeight="1">
-      <c r="A23" s="4" t="inlineStr">
+    <row r="24" ht="24" customHeight="1">
+      <c r="A24" s="39" t="inlineStr">
         <is>
           <t>控件</t>
         </is>
       </c>
-      <c r="C23" s="2" t="inlineStr">
+      <c r="C24" s="37" t="inlineStr">
         <is>
           <t>控件 DSL：类型(参数)，见第四节。</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="30" customHeight="1">
-      <c r="A24" s="4" t="inlineStr">
+    <row r="25" ht="30" customHeight="1">
+      <c r="A25" s="39" t="inlineStr">
         <is>
           <t>附件</t>
         </is>
       </c>
-      <c r="C24" s="2" t="inlineStr">
+      <c r="C25" s="37" t="inlineStr">
         <is>
           <t>预留：上传附件 / 拍照。目前全部留空，后续按需填 拍照(现场;张数) 或 上传(照片,PDF)。</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="30" customHeight="1">
-      <c r="A25" s="4" t="inlineStr">
+    <row r="26" ht="30" customHeight="1">
+      <c r="A26" s="39" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
-      <c r="C25" s="2" t="inlineStr">
+      <c r="C26" s="37" t="inlineStr">
         <is>
           <t>原始表头 + 归一 / 拆分说明，便于审计；「备注」行默认隐藏，不通过时展开。</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="24" customHeight="1">
-      <c r="A27" s="3" t="inlineStr">
+    <row r="28" ht="24" customHeight="1">
+      <c r="A28" s="38" t="inlineStr">
         <is>
           <t>四、控件 DSL（“控件表达”）</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="24" customHeight="1">
-      <c r="A28" s="5" t="inlineStr">
+    <row r="29" ht="24" customHeight="1">
+      <c r="A29" s="40" t="inlineStr">
         <is>
           <t>控件写法</t>
         </is>
       </c>
-      <c r="B28" s="23" t="n"/>
-      <c r="C28" s="5" t="inlineStr">
+      <c r="B29" s="42" t="n"/>
+      <c r="C29" s="40" t="inlineStr">
         <is>
           <t>示例</t>
         </is>
       </c>
-      <c r="D28" s="23" t="n"/>
-      <c r="E28" s="5" t="inlineStr">
+      <c r="D29" s="42" t="n"/>
+      <c r="E29" s="40" t="inlineStr">
         <is>
           <t>含义</t>
         </is>
       </c>
-      <c r="F28" s="23" t="n"/>
-    </row>
-    <row r="29" ht="26" customHeight="1">
-      <c r="A29" s="6" t="inlineStr">
+      <c r="F29" s="42" t="n"/>
+    </row>
+    <row r="30" ht="26" customHeight="1">
+      <c r="A30" s="41" t="inlineStr">
         <is>
           <t>选项(正确;错误项)</t>
         </is>
       </c>
-      <c r="B29" s="23" t="n"/>
-      <c r="C29" s="6" t="inlineStr">
+      <c r="B30" s="42" t="n"/>
+      <c r="C30" s="41" t="inlineStr">
         <is>
           <t>选项(正确;未实施施肥;未达到每株1.5kg)</t>
         </is>
       </c>
-      <c r="D29" s="23" t="n"/>
-      <c r="E29" s="6" t="inlineStr">
+      <c r="D30" s="42" t="n"/>
+      <c r="E30" s="41" t="inlineStr">
         <is>
           <t>单选；第一项为默认；错误项可多个</t>
         </is>
       </c>
-      <c r="F29" s="23" t="n"/>
-    </row>
-    <row r="30" ht="26" customHeight="1">
-      <c r="A30" s="6" t="inlineStr">
+      <c r="F30" s="42" t="n"/>
+    </row>
+    <row r="31" ht="26" customHeight="1">
+      <c r="A31" s="41" t="inlineStr">
+        <is>
+          <t>选项(正确;错误项→备注≥2)</t>
+        </is>
+      </c>
+      <c r="B31" s="42" t="n"/>
+      <c r="C31" s="41" t="inlineStr">
         <is>
           <t>选项(正确;不正确→备注≥2)</t>
         </is>
       </c>
-      <c r="B30" s="23" t="n"/>
-      <c r="C30" s="6" t="inlineStr">
-        <is>
-          <t>选项(正确;不正确→备注≥2)</t>
-        </is>
-      </c>
-      <c r="D30" s="23" t="n"/>
-      <c r="E30" s="6" t="inlineStr">
-        <is>
-          <t>只有「不正确」一个错误项时，选中须填 ≥2 汉字小备注</t>
-        </is>
-      </c>
-      <c r="F30" s="23" t="n"/>
-    </row>
-    <row r="31" ht="26" customHeight="1">
-      <c r="A31" s="6" t="inlineStr">
+      <c r="D31" s="42" t="n"/>
+      <c r="E31" s="41" t="inlineStr">
+        <is>
+          <t>选中带 →备注 的错误项，就在该环节下方展开「备注」文本框，须 ≥2 汉字</t>
+        </is>
+      </c>
+      <c r="F31" s="42" t="n"/>
+    </row>
+    <row r="32" ht="26" customHeight="1">
+      <c r="A32" s="41" t="inlineStr">
         <is>
           <t>按钮(通过;不通过→备注≥2)</t>
         </is>
       </c>
-      <c r="B31" s="23" t="n"/>
-      <c r="C31" s="6" t="inlineStr">
+      <c r="B32" s="42" t="n"/>
+      <c r="C32" s="41" t="inlineStr">
         <is>
           <t>按钮(通过;不通过→备注≥2)</t>
         </is>
       </c>
-      <c r="D31" s="23" t="n"/>
-      <c r="E31" s="6" t="inlineStr">
-        <is>
-          <t>操作按钮；不通过时校验前一行备注 ≥2 汉字</t>
-        </is>
-      </c>
-      <c r="F31" s="23" t="n"/>
-    </row>
-    <row r="32" ht="26" customHeight="1">
-      <c r="A32" s="6" t="inlineStr">
+      <c r="D32" s="42" t="n"/>
+      <c r="E32" s="41" t="inlineStr">
+        <is>
+          <t>操作按钮；不通过时校验流程备注 ≥2 汉字</t>
+        </is>
+      </c>
+      <c r="F32" s="42" t="n"/>
+    </row>
+    <row r="33" ht="26" customHeight="1">
+      <c r="A33" s="41" t="inlineStr">
         <is>
           <t>多选(甲;乙;丙)</t>
         </is>
       </c>
-      <c r="B32" s="23" t="n"/>
-      <c r="C32" s="6" t="inlineStr">
+      <c r="B33" s="42" t="n"/>
+      <c r="C33" s="41" t="inlineStr">
         <is>
           <t>多选(林地清理;底肥放置;…)</t>
         </is>
       </c>
-      <c r="D32" s="23" t="n"/>
-      <c r="E32" s="6" t="inlineStr">
+      <c r="D33" s="42" t="n"/>
+      <c r="E33" s="41" t="inlineStr">
         <is>
           <t>多选勾选</t>
         </is>
       </c>
-      <c r="F32" s="23" t="n"/>
-    </row>
-    <row r="33" ht="26" customHeight="1">
-      <c r="A33" s="6" t="inlineStr">
+      <c r="F33" s="42" t="n"/>
+    </row>
+    <row r="34" ht="26" customHeight="1">
+      <c r="A34" s="41" t="inlineStr">
         <is>
           <t>数值(单位)</t>
         </is>
       </c>
-      <c r="B33" s="23" t="n"/>
-      <c r="C33" s="6" t="inlineStr">
+      <c r="B34" s="42" t="n"/>
+      <c r="C34" s="41" t="inlineStr">
         <is>
           <t>数值(株) / 数值(亩)</t>
         </is>
       </c>
-      <c r="D33" s="23" t="n"/>
-      <c r="E33" s="6" t="inlineStr">
+      <c r="D34" s="42" t="n"/>
+      <c r="E34" s="41" t="inlineStr">
         <is>
           <t>非负数；与设计值自动对照</t>
         </is>
       </c>
-      <c r="F33" s="23" t="n"/>
-    </row>
-    <row r="34" ht="26" customHeight="1">
-      <c r="A34" s="6" t="inlineStr">
+      <c r="F34" s="42" t="n"/>
+    </row>
+    <row r="35" ht="26" customHeight="1">
+      <c r="A35" s="41" t="inlineStr">
+        <is>
+          <t>数值(单位→判断规则)</t>
+        </is>
+      </c>
+      <c r="B35" s="42" t="n"/>
+      <c r="C35" s="41" t="inlineStr">
+        <is>
+          <t>数值(株→≥设计值) / 数值(株→≥设计值×0.95)</t>
+        </is>
+      </c>
+      <c r="D35" s="42" t="n"/>
+      <c r="E35" s="41" t="inlineStr">
+        <is>
+          <t>通过判断：实测满足规则显示「正确」（默认），不满足显示「不正确」并拦住「通过」</t>
+        </is>
+      </c>
+      <c r="F35" s="42" t="n"/>
+    </row>
+    <row r="36" ht="26" customHeight="1">
+      <c r="A36" s="41" t="inlineStr">
         <is>
           <t>百分数(0-100)</t>
         </is>
       </c>
-      <c r="B34" s="23" t="n"/>
-      <c r="C34" s="6" t="inlineStr">
-        <is>
-          <t>百分数(0-100)</t>
-        </is>
-      </c>
-      <c r="D34" s="23" t="n"/>
-      <c r="E34" s="6" t="inlineStr">
-        <is>
-          <t>百分数，0–100</t>
-        </is>
-      </c>
-      <c r="F34" s="23" t="n"/>
-    </row>
-    <row r="35" ht="26" customHeight="1">
-      <c r="A35" s="6" t="inlineStr">
+      <c r="B36" s="42" t="n"/>
+      <c r="C36" s="41" t="inlineStr">
+        <is>
+          <t>百分数(0-100) / 百分数(0-100→≥85)</t>
+        </is>
+      </c>
+      <c r="D36" s="42" t="n"/>
+      <c r="E36" s="41" t="inlineStr">
+        <is>
+          <t>百分数，0–100；可接 →规则 自动判断</t>
+        </is>
+      </c>
+      <c r="F36" s="42" t="n"/>
+    </row>
+    <row r="37" ht="26" customHeight="1">
+      <c r="A37" s="41" t="inlineStr">
         <is>
           <t>文本</t>
         </is>
       </c>
-      <c r="B35" s="23" t="n"/>
-      <c r="C35" s="6" t="inlineStr">
+      <c r="B37" s="42" t="n"/>
+      <c r="C37" s="41" t="inlineStr">
         <is>
           <t>文本</t>
         </is>
       </c>
-      <c r="D35" s="23" t="n"/>
-      <c r="E35" s="6" t="inlineStr">
+      <c r="D37" s="42" t="n"/>
+      <c r="E37" s="41" t="inlineStr">
         <is>
           <t>单行文本</t>
         </is>
       </c>
-      <c r="F35" s="23" t="n"/>
-    </row>
-    <row r="36" ht="26" customHeight="1">
-      <c r="A36" s="6" t="inlineStr">
+      <c r="F37" s="42" t="n"/>
+    </row>
+    <row r="38" ht="26" customHeight="1">
+      <c r="A38" s="41" t="inlineStr">
         <is>
           <t>长文本</t>
         </is>
       </c>
-      <c r="B36" s="23" t="n"/>
-      <c r="C36" s="6" t="inlineStr">
+      <c r="B38" s="42" t="n"/>
+      <c r="C38" s="41" t="inlineStr">
         <is>
           <t>长文本</t>
         </is>
       </c>
-      <c r="D36" s="23" t="n"/>
-      <c r="E36" s="6" t="inlineStr">
+      <c r="D38" s="42" t="n"/>
+      <c r="E38" s="41" t="inlineStr">
         <is>
           <t>多行文本</t>
         </is>
       </c>
-      <c r="F36" s="23" t="n"/>
-    </row>
-    <row r="37" ht="26" customHeight="1">
-      <c r="A37" s="6" t="inlineStr">
+      <c r="F38" s="42" t="n"/>
+    </row>
+    <row r="39" ht="26" customHeight="1">
+      <c r="A39" s="41" t="inlineStr">
         <is>
           <t>自动(公式)</t>
         </is>
       </c>
-      <c r="B37" s="23" t="n"/>
-      <c r="C37" s="6" t="inlineStr">
+      <c r="B39" s="42" t="n"/>
+      <c r="C39" s="41" t="inlineStr">
         <is>
           <t>自动(成活株数/(成活株数+死亡株数)×100%)</t>
         </is>
       </c>
-      <c r="D37" s="23" t="n"/>
-      <c r="E37" s="6" t="inlineStr">
+      <c r="D39" s="42" t="n"/>
+      <c r="E39" s="41" t="inlineStr">
         <is>
           <t>自动计算，不手填</t>
         </is>
       </c>
-      <c r="F37" s="23" t="n"/>
-    </row>
-    <row r="38" ht="26" customHeight="1">
-      <c r="A38" s="6" t="inlineStr">
+      <c r="F39" s="42" t="n"/>
+    </row>
+    <row r="40" ht="26" customHeight="1">
+      <c r="A40" s="41" t="inlineStr">
         <is>
           <t>长文本(隐藏;条件)</t>
         </is>
       </c>
-      <c r="B38" s="23" t="n"/>
-      <c r="C38" s="6" t="inlineStr">
+      <c r="B40" s="42" t="n"/>
+      <c r="C40" s="41" t="inlineStr">
         <is>
           <t>长文本(隐藏;不通过必填≥2汉字)</t>
         </is>
       </c>
-      <c r="D38" s="23" t="n"/>
-      <c r="E38" s="6" t="inlineStr">
+      <c r="D40" s="42" t="n"/>
+      <c r="E40" s="41" t="inlineStr">
         <is>
           <t>默认隐藏；可带条件，如不通过时展开必填</t>
         </is>
       </c>
-      <c r="F38" s="23" t="n"/>
-    </row>
-    <row r="39" ht="26" customHeight="1">
-      <c r="A39" s="6" t="inlineStr">
+      <c r="F40" s="42" t="n"/>
+    </row>
+    <row r="41" ht="26" customHeight="1">
+      <c r="A41" s="41" t="inlineStr">
         <is>
           <t>拍照 / 上传 / 打卡</t>
         </is>
       </c>
-      <c r="B39" s="23" t="n"/>
-      <c r="C39" s="6" t="inlineStr">
+      <c r="B41" s="42" t="n"/>
+      <c r="C41" s="41" t="inlineStr">
         <is>
           <t>拍照(现场;1)</t>
         </is>
       </c>
-      <c r="D39" s="23" t="n"/>
-      <c r="E39" s="6" t="inlineStr">
+      <c r="D41" s="42" t="n"/>
+      <c r="E41" s="41" t="inlineStr">
         <is>
           <t>填在「附件」列，本模板暂未使用</t>
         </is>
       </c>
-      <c r="F39" s="23" t="n"/>
-    </row>
-    <row r="41" ht="24" customHeight="1">
-      <c r="A41" s="3" t="inlineStr">
-        <is>
-          <t>五、选项、按钮与必填</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="24" customHeight="1">
-      <c r="A42" s="2" t="inlineStr">
+      <c r="F41" s="42" t="n"/>
+    </row>
+    <row r="43" ht="24" customHeight="1">
+      <c r="A43" s="38" t="inlineStr">
+        <is>
+          <t>五、通过判断（→规则）</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="30" customHeight="1">
+      <c r="A44" s="37" t="inlineStr">
+        <is>
+          <t>1. 数值 / 百分数 / 自动 控件后面可以接 →规则，例如 数值(株→≥设计值)、百分数(0-100→≥85)。</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="34" customHeight="1">
+      <c r="A45" s="37" t="inlineStr">
+        <is>
+          <t>2. 规则写法：比较符（≥ &gt; ≤ &lt; =）+ 阈值；阈值可以是「设计值」或数字，后面可乘系数（×0.95）或加减偏移（-5）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="40" customHeight="1">
+      <c r="A46" s="37" t="inlineStr">
+        <is>
+          <t>3. 默认「正确」：没填实测值时显示正确；填了以后按规则实时重算。判为「不正确」时不能提交「通过」，现场确实不达标请选「不通过」并写明备注。</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="36" customHeight="1">
+      <c r="A47" s="37" t="inlineStr">
+        <is>
+          <t>4. 不写 →规则 = 不自动判断（与旧模板一致）；规则引用「设计值」但该行没有设计值表头时，提交「通过」会被拦下并提示无法判定。</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="24" customHeight="1">
+      <c r="A49" s="38" t="inlineStr">
+        <is>
+          <t>六、选项、按钮与必填</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="24" customHeight="1">
+      <c r="A50" s="37" t="inlineStr">
         <is>
           <t>1. 选项第一项固定为正向词「正确」，其后为错误项；错误项可以有多个。</t>
         </is>
       </c>
     </row>
-    <row r="43" ht="30" customHeight="1">
-      <c r="A43" s="2" t="inlineStr">
-        <is>
-          <t>2. 只有「不正确」一个错误项时写成 选项(正确;不正确→备注≥2)：选中它必须填 ≥2 汉字小备注。</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="26" customHeight="1">
-      <c r="A44" s="2" t="inlineStr">
+    <row r="51" ht="36" customHeight="1">
+      <c r="A51" s="37" t="inlineStr">
+        <is>
+          <t>2. 错误项可以多个，**每个错误项都写 →备注≥2**（如 选项(正确;未实施施肥→备注≥2;未达到每株1.5kg→备注≥2)）：选中它就在本环节下方展开「备注」文本框，≥2 汉字才能提交。</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="26" customHeight="1">
+      <c r="A52" s="37" t="inlineStr">
         <is>
           <t>3. 可见环节默认必填；「自动」与带「隐藏」的控件不必填，带条件的隐藏项按条件必填。</t>
         </is>
       </c>
     </row>
-    <row r="45" ht="30" customHeight="1">
-      <c r="A45" s="2" t="inlineStr">
-        <is>
-          <t>4. 每个流程最后一行固定为「是否通过」，控件是按钮 通过 / 不通过；其前一行固定为「备注」。</t>
-        </is>
-      </c>
-    </row>
-    <row r="46" ht="26" customHeight="1">
-      <c r="A46" s="2" t="inlineStr">
-        <is>
-          <t>5. 点「通过」直接提交；点「不通过」先校验备注 ≥2 个汉字，通过校验才提交。</t>
-        </is>
-      </c>
-    </row>
-    <row r="48" ht="24" customHeight="1">
-      <c r="A48" s="3" t="inlineStr">
-        <is>
-          <t>六、设计值表头来源</t>
-        </is>
-      </c>
-    </row>
-    <row r="49" ht="30" customHeight="1">
-      <c r="A49" s="2" t="inlineStr">
+    <row r="53" ht="36" customHeight="1">
+      <c r="A53" s="37" t="inlineStr">
+        <is>
+          <t>4. 每个流程最后一行固定为「是否通过」，其前一行固定为「备注」；App 不单独渲染这两行，统一在表单底部显示「通过 / 不通过」两个按钮。</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="36" customHeight="1">
+      <c r="A54" s="37" t="inlineStr">
+        <is>
+          <t>5. 点「通过」= 提交且结论通过；点「不通过」= 展开并校验备注 ≥2 个汉字后再提交。原「提交」按钮已由这两个按钮取代。</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="24" customHeight="1">
+      <c r="A56" s="38" t="inlineStr">
+        <is>
+          <t>七、设计值表头来源</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="30" customHeight="1">
+      <c r="A57" s="37" t="inlineStr">
         <is>
           <t>• 自动匹配：核实密度 → 设计密度（株/亩）、核实株行距 → 设计株行距（米）、核实总株数 → 设计总株数（株）等；按概念匹配，不写死列号。</t>
         </is>
       </c>
     </row>
-    <row r="50" ht="24" customHeight="1">
-      <c r="A50" s="2" t="inlineStr">
+    <row r="58" ht="24" customHeight="1">
+      <c r="A58" s="37" t="inlineStr">
         <is>
           <t>• 常量：有机肥 1.5kg/株、普钙 0.2kg/株、撑杆规格、覆膜质量、回塘质量。</t>
         </is>
       </c>
     </row>
-    <row r="51" ht="24" customHeight="1">
-      <c r="A51" s="2" t="inlineStr">
+    <row r="59" ht="24" customHeight="1">
+      <c r="A59" s="37" t="inlineStr">
         <is>
           <t>• 留空：栽植成活率、样地调查、巡护情况等源表没有设计值的项。</t>
         </is>
       </c>
     </row>
-    <row r="52" ht="26" customHeight="1">
-      <c r="A52" s="2" t="inlineStr">
+    <row r="60" ht="26" customHeight="1">
+      <c r="A60" s="37" t="inlineStr">
         <is>
           <t>• 源表重复表头「核实栽植总株数」按位置区分：栽植总株数 / 树种1 / 树种2。</t>
         </is>
       </c>
     </row>
-    <row r="54" ht="24" customHeight="1">
-      <c r="A54" s="3" t="inlineStr">
-        <is>
-          <t>七、数据口径</t>
-        </is>
-      </c>
-    </row>
-    <row r="55" ht="24" customHeight="1">
-      <c r="A55" s="2" t="inlineStr">
+    <row r="62" ht="24" customHeight="1">
+      <c r="A62" s="38" t="inlineStr">
+        <is>
+          <t>八、数据口径</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="24" customHeight="1">
+      <c r="A63" s="37" t="inlineStr">
         <is>
           <t>• 5 个源 sheet 均 149 行，小班号集合一致；合并为 149 行，无重复行。</t>
         </is>
       </c>
     </row>
-    <row r="56" ht="26" customHeight="1">
-      <c r="A56" s="2" t="inlineStr">
+    <row r="64" ht="26" customHeight="1">
+      <c r="A64" s="37" t="inlineStr">
         <is>
           <t>• 语义重复列合并：设计面积 / 小班面积 → 设计面积（亩）；设计总株数 / 栽植总株数 → 设计总株数（株）。</t>
         </is>
       </c>
     </row>
-    <row r="57" ht="26" customHeight="1">
-      <c r="A57" s="2" t="inlineStr">
+    <row r="65" ht="26" customHeight="1">
+      <c r="A65" s="37" t="inlineStr">
         <is>
           <t>• 单位上移表头；株行距 / 整地规格去掉尾部单位；混交比例全角冒号 → 半角。</t>
         </is>
       </c>
     </row>
-    <row r="58" ht="30" customHeight="1">
-      <c r="A58" s="2" t="inlineStr">
+    <row r="66" ht="30" customHeight="1">
+      <c r="A66" s="37" t="inlineStr">
         <is>
           <t>• 撑杆 / 覆膜原表把数量与规格 / 质量合在一列，流程里拆成「数量（数值）+ 规格 / 质量（选项）」两行。</t>
         </is>
       </c>
     </row>
-    <row r="59" ht="24" customHeight="1">
-      <c r="A59" s="2" t="inlineStr">
-        <is>
-          <t>• 选项正向统一为「正确」，源表错误项保留；只有「不正确」时要求 ≥2 汉字小备注。</t>
-        </is>
-      </c>
-    </row>
-    <row r="60" ht="24" customHeight="1">
-      <c r="A60" s="2" t="inlineStr">
+    <row r="67" ht="30" customHeight="1">
+      <c r="A67" s="37" t="inlineStr">
+        <is>
+          <t>• 选项正向统一为「正确」，源表错误项保留；每个错误项须写 →备注≥2，选中时就地展开文本框。</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="24" customHeight="1">
+      <c r="A68" s="37" t="inlineStr">
         <is>
           <t>• 原始表头完整保留在流程表「备注」列；未删除任何源数据列。</t>
         </is>
       </c>
     </row>
-    <row r="62" ht="24" customHeight="1">
-      <c r="A62" s="3" t="inlineStr">
-        <is>
-          <t>八、解析约定（后续代码）</t>
-        </is>
-      </c>
-    </row>
-    <row r="63" ht="24" customHeight="1">
-      <c r="A63" s="4" t="inlineStr">
+    <row r="70" ht="24" customHeight="1">
+      <c r="A70" s="38" t="inlineStr">
+        <is>
+          <t>九、解析约定（后续代码）</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="24" customHeight="1">
+      <c r="A71" s="39" t="inlineStr">
         <is>
           <t>设计值</t>
         </is>
       </c>
-      <c r="C63" s="2" t="inlineStr">
+      <c r="C71" s="37" t="inlineStr">
         <is>
           <t>第 1 行表头，第 2 行起数据；按「小班号」关联。</t>
         </is>
       </c>
     </row>
-    <row r="64" ht="30" customHeight="1">
-      <c r="A64" s="4" t="inlineStr">
+    <row r="72" ht="30" customHeight="1">
+      <c r="A72" s="39" t="inlineStr">
         <is>
           <t>流程路由</t>
         </is>
       </c>
-      <c r="C64" s="2" t="inlineStr">
+      <c r="C72" s="37" t="inlineStr">
         <is>
           <t>第 1 行表头；按「项目类型」分组、按「序号」排序；前置流程支持 ; 分隔与环检测。</t>
         </is>
       </c>
     </row>
-    <row r="65" ht="24" customHeight="1">
-      <c r="A65" s="4" t="inlineStr">
+    <row r="73" ht="24" customHeight="1">
+      <c r="A73" s="39" t="inlineStr">
         <is>
           <t>流程-*</t>
         </is>
       </c>
-      <c r="C65" s="2" t="inlineStr">
+      <c r="C73" s="37" t="inlineStr">
         <is>
           <t>第 1 行表头，第 2 行起为环节定义；按「序号」排序。</t>
         </is>
       </c>
     </row>
-    <row r="66" ht="30" customHeight="1">
-      <c r="A66" s="4" t="inlineStr">
+    <row r="74" ht="36" customHeight="1">
+      <c r="A74" s="39" t="inlineStr">
         <is>
           <t>控件</t>
         </is>
       </c>
-      <c r="C66" s="2" t="inlineStr">
-        <is>
-          <t>取「(」前的类型；选项 / 按钮用半角分号分隔，「→」后是选中该项的附加规则（如 备注≥2）。</t>
-        </is>
-      </c>
-    </row>
-    <row r="67" ht="30" customHeight="1">
-      <c r="A67" s="4" t="inlineStr">
+      <c r="C74" s="37" t="inlineStr">
+        <is>
+          <t>取「(」前的类型；选项 / 按钮用半角分号分隔，「→」后是附加规则：选项 → 备注≥2（就地展开备注），数值 → ≥设计值 / ≥85（通过判断）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="40" customHeight="1">
+      <c r="A75" s="39" t="inlineStr">
         <is>
           <t>结论行</t>
         </is>
       </c>
-      <c r="C67" s="2" t="inlineStr">
-        <is>
-          <t>最后一行「是否通过」= 按钮(通过;不通过→备注≥2)；其前一行「备注」必填 ≥2 汉字。</t>
-        </is>
-      </c>
-    </row>
-    <row r="68" ht="30" customHeight="1">
-      <c r="A68" s="4" t="inlineStr">
+      <c r="C75" s="37" t="inlineStr">
+        <is>
+          <t>最后一行「是否通过」= 按钮(通过;不通过→备注≥2)；其前一行「备注」必填 ≥2 汉字；App 底部统一渲染「通过 / 不通过」提交，不重复显示这两行。</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="30" customHeight="1">
+      <c r="A76" s="39" t="inlineStr">
         <is>
           <t>设计值表头引用</t>
         </is>
       </c>
-      <c r="C68" s="2" t="inlineStr">
+      <c r="C76" s="37" t="inlineStr">
         <is>
           <t>命中「设计值」sheet 表头 → 取当前小班值；以「常量：」开头 → 原样展示；空 → 无。</t>
         </is>
       </c>
     </row>
-    <row r="69" ht="30" customHeight="1">
-      <c r="A69" s="4" t="inlineStr">
+    <row r="77" ht="30" customHeight="1">
+      <c r="A77" s="39" t="inlineStr">
         <is>
           <t>不改字段</t>
         </is>
       </c>
-      <c r="C69" s="2" t="inlineStr">
+      <c r="C77" s="37" t="inlineStr">
         <is>
           <t>新增源表 sheet / 列后重新运行 tools/tpl_tool.py build；代码按列语义读，不写死项目字段。</t>
         </is>
       </c>
     </row>
-    <row r="70" ht="24" customHeight="1">
-      <c r="A70" s="4" t="inlineStr">
+    <row r="78" ht="30" customHeight="1">
+      <c r="A78" s="39" t="inlineStr">
         <is>
           <t>命令</t>
         </is>
       </c>
-      <c r="C70" s="2" t="inlineStr">
-        <is>
-          <t>python3 tools/tpl_tool.py build  |  python3 tools/tpl_tool.py show --file &lt;模板.xlsx&gt;</t>
+      <c r="C78" s="37" t="inlineStr">
+        <is>
+          <t>python3 tools/tpl/tpl_tool.py build  |  params [--file &lt;模板.xlsx&gt;] [--force]  |  show --file &lt;模板.xlsx&gt;</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="108">
+  <mergeCells count="118">
     <mergeCell ref="A15:B15"/>
-    <mergeCell ref="A64:B64"/>
+    <mergeCell ref="A66:F66"/>
+    <mergeCell ref="A73:B73"/>
+    <mergeCell ref="C72:F72"/>
     <mergeCell ref="A50:F50"/>
-    <mergeCell ref="A70:B70"/>
     <mergeCell ref="A3:F3"/>
-    <mergeCell ref="A55:F55"/>
+    <mergeCell ref="A47:F47"/>
+    <mergeCell ref="C78:F78"/>
     <mergeCell ref="A7:B7"/>
+    <mergeCell ref="A41:B41"/>
     <mergeCell ref="A5:F5"/>
+    <mergeCell ref="C41:D41"/>
     <mergeCell ref="C6:F6"/>
     <mergeCell ref="C15:F15"/>
+    <mergeCell ref="A74:B74"/>
+    <mergeCell ref="A20:F20"/>
     <mergeCell ref="C24:F24"/>
     <mergeCell ref="E34:F34"/>
-    <mergeCell ref="C64:F64"/>
     <mergeCell ref="A13:F13"/>
+    <mergeCell ref="C73:F73"/>
     <mergeCell ref="A44:F44"/>
     <mergeCell ref="A33:B33"/>
+    <mergeCell ref="C26:F26"/>
+    <mergeCell ref="A76:B76"/>
     <mergeCell ref="C36:D36"/>
     <mergeCell ref="A58:F58"/>
     <mergeCell ref="E36:F36"/>
-    <mergeCell ref="C63:F63"/>
     <mergeCell ref="A17:B17"/>
+    <mergeCell ref="C10:F10"/>
+    <mergeCell ref="A64:F64"/>
     <mergeCell ref="A22:B22"/>
     <mergeCell ref="A35:B35"/>
     <mergeCell ref="A51:F51"/>
     <mergeCell ref="A60:F60"/>
-    <mergeCell ref="A68:B68"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="A70:F70"/>
     <mergeCell ref="A9:B9"/>
     <mergeCell ref="A39:B39"/>
-    <mergeCell ref="A41:F41"/>
     <mergeCell ref="A30:B30"/>
     <mergeCell ref="C17:F17"/>
     <mergeCell ref="C30:D30"/>
-    <mergeCell ref="A27:F27"/>
-    <mergeCell ref="C67:F67"/>
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="E38:F38"/>
-    <mergeCell ref="A42:F42"/>
-    <mergeCell ref="C69:F69"/>
     <mergeCell ref="A37:B37"/>
+    <mergeCell ref="C40:D40"/>
     <mergeCell ref="A62:F62"/>
-    <mergeCell ref="C14:F14"/>
-    <mergeCell ref="A48:F48"/>
+    <mergeCell ref="E40:F40"/>
+    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="A28:F28"/>
+    <mergeCell ref="A71:B71"/>
     <mergeCell ref="A8:B8"/>
     <mergeCell ref="A59:F59"/>
-    <mergeCell ref="A11:F11"/>
-    <mergeCell ref="A63:B63"/>
+    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="C71:F71"/>
+    <mergeCell ref="A77:B77"/>
     <mergeCell ref="A34:B34"/>
+    <mergeCell ref="C76:F76"/>
     <mergeCell ref="C34:D34"/>
     <mergeCell ref="A54:F54"/>
     <mergeCell ref="A46:F46"/>
@@ -15916,20 +16093,19 @@
     <mergeCell ref="A36:B36"/>
     <mergeCell ref="A56:F56"/>
     <mergeCell ref="E39:F39"/>
-    <mergeCell ref="C66:F66"/>
-    <mergeCell ref="A69:B69"/>
+    <mergeCell ref="C18:F18"/>
+    <mergeCell ref="A78:B78"/>
     <mergeCell ref="C29:D29"/>
     <mergeCell ref="E29:F29"/>
-    <mergeCell ref="A65:B65"/>
-    <mergeCell ref="C68:F68"/>
+    <mergeCell ref="C77:F77"/>
+    <mergeCell ref="A75:B75"/>
     <mergeCell ref="C31:D31"/>
+    <mergeCell ref="A53:F53"/>
     <mergeCell ref="E31:F31"/>
+    <mergeCell ref="A63:F63"/>
     <mergeCell ref="A21:B21"/>
-    <mergeCell ref="A19:F19"/>
-    <mergeCell ref="C20:F20"/>
+    <mergeCell ref="A68:F68"/>
     <mergeCell ref="A32:B32"/>
-    <mergeCell ref="A14:B14"/>
-    <mergeCell ref="C65:F65"/>
     <mergeCell ref="A23:B23"/>
     <mergeCell ref="C22:F22"/>
     <mergeCell ref="A49:F49"/>
@@ -15938,10 +16114,11 @@
     <mergeCell ref="C38:D38"/>
     <mergeCell ref="E32:F32"/>
     <mergeCell ref="A1:F1"/>
+    <mergeCell ref="E41:F41"/>
     <mergeCell ref="A45:F45"/>
     <mergeCell ref="C21:F21"/>
-    <mergeCell ref="A67:B67"/>
-    <mergeCell ref="C70:F70"/>
+    <mergeCell ref="A40:B40"/>
+    <mergeCell ref="A65:F65"/>
     <mergeCell ref="A24:B24"/>
     <mergeCell ref="C23:F23"/>
     <mergeCell ref="C33:D33"/>
@@ -15954,25 +16131,28 @@
     <mergeCell ref="E35:F35"/>
     <mergeCell ref="A16:B16"/>
     <mergeCell ref="A25:B25"/>
-    <mergeCell ref="E28:F28"/>
-    <mergeCell ref="A66:B66"/>
+    <mergeCell ref="A14:F14"/>
+    <mergeCell ref="A18:B18"/>
     <mergeCell ref="A43:F43"/>
+    <mergeCell ref="C74:F74"/>
     <mergeCell ref="A52:F52"/>
     <mergeCell ref="E30:F30"/>
+    <mergeCell ref="A67:F67"/>
     <mergeCell ref="C16:F16"/>
     <mergeCell ref="C25:F25"/>
     <mergeCell ref="C39:D39"/>
     <mergeCell ref="C9:F9"/>
-    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="A72:B72"/>
     <mergeCell ref="A29:B29"/>
+    <mergeCell ref="C75:F75"/>
     <mergeCell ref="C37:D37"/>
     <mergeCell ref="E37:F37"/>
     <mergeCell ref="A31:B31"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="portrait" paperSize="9" fitToHeight="2"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="2" fitToWidth="1"/>
   <rowBreaks count="1" manualBreakCount="1">
-    <brk id="48" min="0" max="16383" man="1"/>
+    <brk id="56" min="0" max="16383" man="1"/>
   </rowBreaks>
 </worksheet>
 </file>
@@ -15984,7 +16164,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -16028,18 +16208,18 @@
       </c>
     </row>
     <row r="2" ht="30" customHeight="1">
-      <c r="A2" s="28" t="inlineStr">
+      <c r="A2" s="32" t="inlineStr">
         <is>
           <t>可编辑列</t>
         </is>
       </c>
       <c r="B2" s="26" t="inlineStr"/>
-      <c r="C2" s="29" t="inlineStr">
+      <c r="C2" s="33" t="inlineStr">
         <is>
           <t>列表</t>
         </is>
       </c>
-      <c r="D2" s="29" t="inlineStr"/>
+      <c r="D2" s="33" t="inlineStr"/>
       <c r="E2" s="26" t="inlineStr">
         <is>
           <t>v2 界面不显示数据网格，留空；以后若要开网格再填列名。</t>
@@ -16048,116 +16228,268 @@
       <c r="F2" s="26" t="inlineStr"/>
     </row>
     <row r="3" ht="30" customHeight="1">
-      <c r="A3" s="28" t="inlineStr">
+      <c r="A3" s="32" t="inlineStr">
         <is>
           <t>功能</t>
         </is>
       </c>
       <c r="B3" s="26" t="inlineStr"/>
-      <c r="C3" s="29" t="inlineStr">
+      <c r="C3" s="33" t="inlineStr">
         <is>
           <t>列表</t>
         </is>
       </c>
-      <c r="D3" s="29" t="inlineStr"/>
+      <c r="D3" s="33" t="inlineStr"/>
       <c r="E3" s="26" t="inlineStr">
         <is>
           <t>拍照 / 视频 / 轨迹 / 打卡；开了拍照/视频还要补三条拍摄模板 key。</t>
         </is>
       </c>
-      <c r="F3" s="26" t="inlineStr"/>
+      <c r="F3" s="26" t="inlineStr">
+        <is>
+          <t>拍照;轨迹</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="28" t="inlineStr">
+      <c r="A4" s="32" t="inlineStr">
+        <is>
+          <t>相片备注</t>
+        </is>
+      </c>
+      <c r="B4" s="26" t="inlineStr">
+        <is>
+          <t>{{项目类型}}{{标段}}{{乡（镇）}}{{村（社区）}}{{小班号}}小班</t>
+        </is>
+      </c>
+      <c r="C4" s="33" t="inlineStr">
+        <is>
+          <t>模板</t>
+        </is>
+      </c>
+      <c r="D4" s="33" t="inlineStr">
+        <is>
+          <t>{{项目类型}}{{标段}}{{乡（镇）}}{{村（社区）}}{{小班号}}小班</t>
+        </is>
+      </c>
+      <c r="E4" s="26" t="inlineStr">
+        <is>
+          <t>照片水印正文（首行时间戳固定，C06 不参数化）；{{列名}}取当前小班行。</t>
+        </is>
+      </c>
+      <c r="F4" s="26" t="inlineStr"/>
+    </row>
+    <row r="5" ht="30" customHeight="1">
+      <c r="A5" s="32" t="inlineStr">
+        <is>
+          <t>相片文件名</t>
+        </is>
+      </c>
+      <c r="B5" s="26" t="inlineStr">
+        <is>
+          <t>{{标段}}_{{小班号}}_{{时间}}</t>
+        </is>
+      </c>
+      <c r="C5" s="33" t="inlineStr">
+        <is>
+          <t>模板</t>
+        </is>
+      </c>
+      <c r="D5" s="33" t="inlineStr">
+        <is>
+          <t>{{标段}}_{{小班号}}_{{时间}}</t>
+        </is>
+      </c>
+      <c r="E5" s="26" t="inlineStr">
+        <is>
+          <t>照片文件名（不含扩展名）；{{时间}}=YYYYMMDD_HHMMSS。</t>
+        </is>
+      </c>
+      <c r="F5" s="26" t="inlineStr"/>
+    </row>
+    <row r="6" ht="30" customHeight="1">
+      <c r="A6" s="32" t="inlineStr">
+        <is>
+          <t>目录</t>
+        </is>
+      </c>
+      <c r="B6" s="26" t="inlineStr">
+        <is>
+          <t>{{项目类型}}/{{标段}}/{{小班号}}</t>
+        </is>
+      </c>
+      <c r="C6" s="33" t="inlineStr">
+        <is>
+          <t>模板</t>
+        </is>
+      </c>
+      <c r="D6" s="33" t="inlineStr">
+        <is>
+          <t>{{项目类型}}/{{标段}}/{{小班号}}</t>
+        </is>
+      </c>
+      <c r="E6" s="26" t="inlineStr">
+        <is>
+          <t>照片在本机相册的子目录：Pictures/{目录}/；半角 / 分层。</t>
+        </is>
+      </c>
+      <c r="F6" s="26" t="inlineStr"/>
+    </row>
+    <row r="7" ht="30" customHeight="1">
+      <c r="A7" s="32" t="inlineStr">
+        <is>
+          <t>压缩最长边</t>
+        </is>
+      </c>
+      <c r="B7" s="26" t="inlineStr">
+        <is>
+          <t>1440</t>
+        </is>
+      </c>
+      <c r="C7" s="33" t="inlineStr">
+        <is>
+          <t>数值</t>
+        </is>
+      </c>
+      <c r="D7" s="33" t="inlineStr">
+        <is>
+          <t>1440</t>
+        </is>
+      </c>
+      <c r="E7" s="26" t="inlineStr">
+        <is>
+          <t>手机端压缩最长边(px)，300-8000，仅影响新拍照片。</t>
+        </is>
+      </c>
+      <c r="F7" s="26" t="inlineStr">
+        <is>
+          <t>1440</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="30" customHeight="1">
+      <c r="A8" s="32" t="inlineStr">
+        <is>
+          <t>压缩质量</t>
+        </is>
+      </c>
+      <c r="B8" s="26" t="inlineStr">
+        <is>
+          <t>0.8</t>
+        </is>
+      </c>
+      <c r="C8" s="33" t="inlineStr">
+        <is>
+          <t>数值</t>
+        </is>
+      </c>
+      <c r="D8" s="33" t="inlineStr">
+        <is>
+          <t>0.8</t>
+        </is>
+      </c>
+      <c r="E8" s="26" t="inlineStr">
+        <is>
+          <t>JPEG 质量 0.1-1，仅影响新拍照片；建议 0.75-0.82。</t>
+        </is>
+      </c>
+      <c r="F8" s="26" t="inlineStr">
+        <is>
+          <t>0.8</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="30" customHeight="1">
+      <c r="A9" s="32" t="inlineStr">
         <is>
           <t>搜索选项</t>
         </is>
       </c>
-      <c r="B4" s="26" t="inlineStr">
+      <c r="B9" s="26" t="inlineStr">
         <is>
           <t>项目类型|select;标段|select;乡（镇）|select;村（社区）|select;小班号|search</t>
         </is>
       </c>
-      <c r="C4" s="29" t="inlineStr">
+      <c r="C9" s="33" t="inlineStr">
         <is>
           <t>控件映射</t>
         </is>
       </c>
-      <c r="D4" s="29" t="inlineStr">
+      <c r="D9" s="33" t="inlineStr">
         <is>
           <t>项目类型|select;标段|select;乡（镇）|select;村（社区）|select;小班号|search</t>
         </is>
       </c>
-      <c r="E4" s="26" t="inlineStr">
+      <c r="E9" s="26" t="inlineStr">
         <is>
           <t>选择栏字段|控件类型；顺序即级联顺序，前面的选择过滤后面的候选，小班放最后。</t>
         </is>
       </c>
-      <c r="F4" s="26" t="inlineStr">
+      <c r="F9" s="26" t="inlineStr">
         <is>
           <t>项目类型|select;标段|select;乡（镇）|select;村（社区）|select;小班号|search</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="30" customHeight="1">
-      <c r="A5" s="28" t="inlineStr">
+    <row r="10" ht="30" customHeight="1">
+      <c r="A10" s="32" t="inlineStr">
         <is>
           <t>unique-key</t>
         </is>
       </c>
-      <c r="B5" s="26" t="inlineStr">
+      <c r="B10" s="26" t="inlineStr">
         <is>
           <t>小班号</t>
         </is>
       </c>
-      <c r="C5" s="29" t="inlineStr">
+      <c r="C10" s="33" t="inlineStr">
         <is>
           <t>文本</t>
         </is>
       </c>
-      <c r="D5" s="29" t="inlineStr">
+      <c r="D10" s="33" t="inlineStr">
         <is>
           <t>小班号</t>
         </is>
       </c>
-      <c r="E5" s="26" t="inlineStr">
+      <c r="E10" s="26" t="inlineStr">
         <is>
           <t>行标识列；必须非空且唯一，且不能出现在可编辑列。</t>
         </is>
       </c>
-      <c r="F5" s="26" t="inlineStr">
+      <c r="F10" s="26" t="inlineStr">
         <is>
           <t>小班号</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="30" customHeight="1">
-      <c r="A6" s="28" t="inlineStr">
+    <row r="11" ht="30" customHeight="1">
+      <c r="A11" s="32" t="inlineStr">
         <is>
           <t>导出筛选</t>
         </is>
       </c>
-      <c r="B6" s="26" t="inlineStr">
+      <c r="B11" s="26" t="inlineStr">
         <is>
           <t>项目类型|select;标段|select</t>
         </is>
       </c>
-      <c r="C6" s="29" t="inlineStr">
+      <c r="C11" s="33" t="inlineStr">
         <is>
           <t>控件映射</t>
         </is>
       </c>
-      <c r="D6" s="29" t="inlineStr">
+      <c r="D11" s="33" t="inlineStr">
         <is>
           <t>项目类型|select;标段|select</t>
         </is>
       </c>
-      <c r="E6" s="26" t="inlineStr">
+      <c r="E11" s="26" t="inlineStr">
         <is>
           <t>后台下载 Excel 的筛选弹框字段（只筛行）。</t>
         </is>
       </c>
-      <c r="F6" s="26" t="inlineStr">
+      <c r="F11" s="26" t="inlineStr">
         <is>
           <t>项目类型|select;标段|select</t>
         </is>

--- a/data/tpl-人工造林-验收流程模板.xlsx
+++ b/data/tpl-人工造林-验收流程模板.xlsx
@@ -13856,10 +13856,14 @@
           <t>选项(正确;不正确→备注≥2)</t>
         </is>
       </c>
-      <c r="E2" s="10" t="n"/>
+      <c r="E2" s="10" t="inlineStr">
+        <is>
+          <t>拍照:施工面积@1</t>
+        </is>
+      </c>
       <c r="F2" s="12" t="inlineStr">
         <is>
-          <t>原表头：核实施工面积(1.已实施完成2.未实施完成)；「正确」在首位；选「不正确」须填 ≥2 汉字小备注。</t>
+          <t>原表头：核实施工面积(1.已实施完成2.未实施完成)。</t>
         </is>
       </c>
     </row>
@@ -13885,7 +13889,7 @@
       <c r="E3" s="10" t="n"/>
       <c r="F3" s="12" t="inlineStr">
         <is>
-          <t>原表头：核实密度（1.达标2.未达标）；「正确」在首位；选「不正确」须填 ≥2 汉字小备注。</t>
+          <t>原表头：核实密度（1.达标2.未达标）。</t>
         </is>
       </c>
     </row>
@@ -13960,7 +13964,11 @@
           <t>文本</t>
         </is>
       </c>
-      <c r="E6" s="10" t="n"/>
+      <c r="E6" s="10" t="inlineStr">
+        <is>
+          <t>拍照:整地规格@1</t>
+        </is>
+      </c>
       <c r="F6" s="12" t="inlineStr">
         <is>
           <t>原表头：核实整地规格（按实际测量填写）；按实际填写。</t>
@@ -13989,7 +13997,7 @@
       <c r="E7" s="10" t="n"/>
       <c r="F7" s="12" t="inlineStr">
         <is>
-          <t>原表头：核实总数量（按实际测量填写）；按数值填写，与设计值自动对照。 通过判断：≥设计值</t>
+          <t>原表头：核实总数量（按实际测量填写）；按实测填写，与设计值自动对照。</t>
         </is>
       </c>
     </row>
@@ -14117,7 +14125,7 @@
       <c r="E2" s="10" t="n"/>
       <c r="F2" s="12" t="inlineStr">
         <is>
-          <t>原表头：核实施工面积(1.已实施完成2.未实施完成)；「正确」在首位；选「不正确」须填 ≥2 汉字小备注。</t>
+          <t>原表头：核实施工面积(1.已实施完成2.未实施完成)。</t>
         </is>
       </c>
     </row>
@@ -14143,7 +14151,7 @@
       <c r="E3" s="10" t="n"/>
       <c r="F3" s="12" t="inlineStr">
         <is>
-          <t>原表头：有机肥1.5kg/株(1.已实施施肥2.未实施施肥3.达到每株1.5kg4.未达到每株1.5kg )；「正确」在首位，其余为错误项，选中后须在本环节填 ≥2 汉字备注。</t>
+          <t>原表头：有机肥1.5kg/株(1.已实施施肥2.未实施施肥3.达到每株1.5kg4.未达到每株1.5kg )。</t>
         </is>
       </c>
     </row>
@@ -14169,7 +14177,7 @@
       <c r="E4" s="10" t="n"/>
       <c r="F4" s="12" t="inlineStr">
         <is>
-          <t>原表头：普钙0.2kg/株(1.已实施施肥2.未实施施肥3.达到每株0.2kg4.未达到每株0.2kg )；「正确」在首位，其余为错误项，选中后须在本环节填 ≥2 汉字备注。</t>
+          <t>原表头：普钙0.2kg/株(1.已实施施肥2.未实施施肥3.达到每株0.2kg4.未达到每株0.2kg )。</t>
         </is>
       </c>
     </row>
@@ -14192,10 +14200,14 @@
           <t>选项(正确;不正确→备注≥2)</t>
         </is>
       </c>
-      <c r="E5" s="10" t="n"/>
+      <c r="E5" s="10" t="inlineStr">
+        <is>
+          <t>拍照:回塘质量@1</t>
+        </is>
+      </c>
       <c r="F5" s="12" t="inlineStr">
         <is>
-          <t>原表头：回塘质量（1.质量达标2.质量不达标）；「正确」在首位；选「不正确」须填 ≥2 汉字小备注。</t>
+          <t>原表头：回塘质量（1.质量达标2.质量不达标）。</t>
         </is>
       </c>
     </row>
@@ -14320,10 +14332,14 @@
           <t>选项(正确;不正确→备注≥2)</t>
         </is>
       </c>
-      <c r="E2" s="10" t="n"/>
+      <c r="E2" s="10" t="inlineStr">
+        <is>
+          <t>拍照:栽植面积@1</t>
+        </is>
+      </c>
       <c r="F2" s="12" t="inlineStr">
         <is>
-          <t>原表头：核实栽植面积(1.已实施完成2.未实施完成)；「正确」在首位；选「不正确」须填 ≥2 汉字小备注。</t>
+          <t>原表头：核实栽植面积(1.已实施完成2.未实施完成)。</t>
         </is>
       </c>
     </row>
@@ -14349,7 +14365,7 @@
       <c r="E3" s="10" t="n"/>
       <c r="F3" s="12" t="inlineStr">
         <is>
-          <t>原表头：核实造林树种（1一致2.不一致（填写实际树种））；「正确」在首位；选「不正确」须填 ≥2 汉字小备注。</t>
+          <t>原表头：核实造林树种（1一致2.不一致（填写实际树种））。</t>
         </is>
       </c>
     </row>
@@ -14375,7 +14391,7 @@
       <c r="E4" s="10" t="n"/>
       <c r="F4" s="12" t="inlineStr">
         <is>
-          <t>原表头：核实混交方式（1.带状2.非带状（填写实际混交方式））；「正确」在首位；选「不正确」须填 ≥2 汉字小备注。</t>
+          <t>原表头：核实混交方式（1.带状2.非带状（填写实际混交方式））。</t>
         </is>
       </c>
     </row>
@@ -14401,7 +14417,7 @@
       <c r="E5" s="10" t="n"/>
       <c r="F5" s="12" t="inlineStr">
         <is>
-          <t>原表头：核实混交比例（1.符合2.不符合（填写实际混交比例））；「正确」在首位；选「不正确」须填 ≥2 汉字小备注。</t>
+          <t>原表头：核实混交比例（1.符合2.不符合（填写实际混交比例））。</t>
         </is>
       </c>
     </row>
@@ -14424,10 +14440,14 @@
           <t>数值(株→≥设计值)</t>
         </is>
       </c>
-      <c r="E6" s="10" t="n"/>
+      <c r="E6" s="10" t="inlineStr">
+        <is>
+          <t>拍照:栽植株数@1</t>
+        </is>
+      </c>
       <c r="F6" s="12" t="inlineStr">
         <is>
-          <t>原表头：核实栽植总株数（1.达标2.不达标（填写实际数量））；按数值填写，与设计值自动对照。 通过判断：≥设计值</t>
+          <t>原表头：核实栽植总株数（1.达标2.不达标（填写实际数量））；按实测填写，与设计值自动对照。</t>
         </is>
       </c>
     </row>
@@ -14453,7 +14473,7 @@
       <c r="E7" s="10" t="n"/>
       <c r="F7" s="12" t="inlineStr">
         <is>
-          <t>源表同名列第 2 次出现，按列位置取「树种1株数（株）」。原表头：核实栽植总株数（1.达标2.不达标（填写实际数量））；按数值填写，与设计值自动对照。 通过判断：≥设计值</t>
+          <t>源表同名列第 2 次出现，按列位置取「树种1株数（株）」。原表头：核实栽植总株数（1.达标2.不达标（填写实际数量））；按实测填写，与设计值自动对照。</t>
         </is>
       </c>
     </row>
@@ -14479,7 +14499,7 @@
       <c r="E8" s="10" t="n"/>
       <c r="F8" s="12" t="inlineStr">
         <is>
-          <t>源表同名列第 3 次出现，按列位置取「树种2株数（株）」。原表头：核实栽植总株数（1.达标2.不达标（填写实际数量））；按数值填写，与设计值自动对照。 通过判断：≥设计值</t>
+          <t>源表同名列第 3 次出现，按列位置取「树种2株数（株）」。原表头：核实栽植总株数（1.达标2.不达标（填写实际数量））；按实测填写，与设计值自动对照。</t>
         </is>
       </c>
     </row>
@@ -14499,13 +14519,13 @@
       </c>
       <c r="D9" s="10" t="inlineStr">
         <is>
-          <t>数值(株→≥设计值)</t>
+          <t>数值(根→≥设计值)</t>
         </is>
       </c>
       <c r="E9" s="10" t="n"/>
       <c r="F9" s="12" t="inlineStr">
         <is>
-          <t>原表头：核实撑杆数量（1.数量达标2.数量不达标（填写实际数量）3.撑杆规格达标4.撑杆规格不达标）；原表把数量与规格合在一列，这里拆成「核实撑杆数量（数值）+ 撑杆规格（选项）」两行。 通过判断：≥设计值</t>
+          <t>原表头：核实撑杆数量（1.数量达标2.数量不达标（填写实际数量）3.撑杆规格达标4.撑杆规格不达标）；原表把数量与规格合在一列，这里拆成「核实撑杆数量（数值）+ 撑杆规格（选项）」两行。</t>
         </is>
       </c>
     </row>
@@ -14531,7 +14551,7 @@
       <c r="E10" s="10" t="n"/>
       <c r="F10" s="12" t="inlineStr">
         <is>
-          <t>原表头：核实撑杆数量（1.数量达标2.数量不达标（填写实际数量）3.撑杆规格达标4.撑杆规格不达标）；原表把数量与规格合在一列，这里拆成「核实撑杆数量（数值）+ 撑杆规格（选项）」两行。 选「不正确」须填 ≥2 汉字小备注。</t>
+          <t>原表头：核实撑杆数量（1.数量达标2.数量不达标（填写实际数量）3.撑杆规格达标4.撑杆规格不达标）；原表把数量与规格合在一列，这里拆成「核实撑杆数量（数值）+ 撑杆规格（选项）」两行。</t>
         </is>
       </c>
     </row>
@@ -14557,7 +14577,7 @@
       <c r="E11" s="10" t="n"/>
       <c r="F11" s="12" t="inlineStr">
         <is>
-          <t>原表头：核实覆膜数量（1.数量达标2.数量不达标（填写实际数量）3.覆膜质量达标4.覆膜质量不达标）；原表把数量与质量合在一列，这里拆成「核实覆膜数量（数值）+ 覆膜质量（选项）」两行。 通过判断：≥设计值</t>
+          <t>原表头：核实覆膜数量（1.数量达标2.数量不达标（填写实际数量）3.覆膜质量达标4.覆膜质量不达标）；原表把数量与质量合在一列，这里拆成「核实覆膜数量（数值）+ 覆膜质量（选项）」两行。</t>
         </is>
       </c>
     </row>
@@ -14583,7 +14603,7 @@
       <c r="E12" s="10" t="n"/>
       <c r="F12" s="12" t="inlineStr">
         <is>
-          <t>原表头：核实覆膜数量（1.数量达标2.数量不达标（填写实际数量）3.覆膜质量达标4.覆膜质量不达标）；原表把数量与质量合在一列，这里拆成「核实覆膜数量（数值）+ 覆膜质量（选项）」两行。 选「不正确」须填 ≥2 汉字小备注。</t>
+          <t>原表头：核实覆膜数量（1.数量达标2.数量不达标（填写实际数量）3.覆膜质量达标4.覆膜质量不达标）；原表把数量与质量合在一列，这里拆成「核实覆膜数量（数值）+ 覆膜质量（选项）」两行。</t>
         </is>
       </c>
     </row>
@@ -14711,7 +14731,7 @@
       <c r="E2" s="10" t="n"/>
       <c r="F2" s="12" t="inlineStr">
         <is>
-          <t>原表头：核实栽植面积(1.已实施完成2.未实施完成)；「正确」在首位；选「不正确」须填 ≥2 汉字小备注。</t>
+          <t>原表头：核实栽植面积(1.已实施完成2.未实施完成)。</t>
         </is>
       </c>
     </row>
@@ -14737,7 +14757,7 @@
       <c r="E3" s="10" t="n"/>
       <c r="F3" s="12" t="inlineStr">
         <is>
-          <t>原表头：核实造林树种（1一致2.不一致（填写实际树种））；「正确」在首位；选「不正确」须填 ≥2 汉字小备注。</t>
+          <t>原表头：核实造林树种（1一致2.不一致（填写实际树种））。</t>
         </is>
       </c>
     </row>
@@ -14763,7 +14783,7 @@
       <c r="E4" s="10" t="n"/>
       <c r="F4" s="12" t="inlineStr">
         <is>
-          <t>原表头：核实混交方式（1.带状2.非带状（填写实际混交方式））；「正确」在首位；选「不正确」须填 ≥2 汉字小备注。</t>
+          <t>原表头：核实混交方式（1.带状2.非带状（填写实际混交方式））。</t>
         </is>
       </c>
     </row>
@@ -14789,7 +14809,7 @@
       <c r="E5" s="10" t="n"/>
       <c r="F5" s="12" t="inlineStr">
         <is>
-          <t>原表头：核实混交比例（1.符合2.不符合（填写实际混交比例））；「正确」在首位；选「不正确」须填 ≥2 汉字小备注。</t>
+          <t>原表头：核实混交比例（1.符合2.不符合（填写实际混交比例））。</t>
         </is>
       </c>
     </row>
@@ -14815,7 +14835,7 @@
       <c r="E6" s="10" t="n"/>
       <c r="F6" s="12" t="inlineStr">
         <is>
-          <t>原表头：核实栽植总株数（1.达标2.不达标（填写实际数量））；按数值填写，与设计值自动对照。 通过判断：≥设计值</t>
+          <t>原表头：核实栽植总株数（1.达标2.不达标（填写实际数量））；按实测填写，与设计值自动对照。</t>
         </is>
       </c>
     </row>
@@ -14841,7 +14861,7 @@
       <c r="E7" s="10" t="n"/>
       <c r="F7" s="12" t="inlineStr">
         <is>
-          <t>源表同名列第 2 次出现，按列位置取「树种1株数（株）」。原表头：核实栽植总株数（1.达标2.不达标（填写实际数量））；按数值填写，与设计值自动对照。 通过判断：≥设计值</t>
+          <t>源表同名列第 2 次出现，按列位置取「树种1株数（株）」。原表头：核实栽植总株数（1.达标2.不达标（填写实际数量））；按实测填写，与设计值自动对照。</t>
         </is>
       </c>
     </row>
@@ -14867,7 +14887,7 @@
       <c r="E8" s="10" t="n"/>
       <c r="F8" s="12" t="inlineStr">
         <is>
-          <t>源表同名列第 3 次出现，按列位置取「树种2株数（株）」。原表头：核实栽植总株数（1.达标2.不达标（填写实际数量））；按数值填写，与设计值自动对照。 通过判断：≥设计值</t>
+          <t>源表同名列第 3 次出现，按列位置取「树种2株数（株）」。原表头：核实栽植总株数（1.达标2.不达标（填写实际数量））；按实测填写，与设计值自动对照。</t>
         </is>
       </c>
     </row>
@@ -14886,10 +14906,14 @@
           <t>百分数(0-100→≥85)</t>
         </is>
       </c>
-      <c r="E9" s="10" t="n"/>
+      <c r="E9" s="10" t="inlineStr">
+        <is>
+          <t>拍照:成活率抽查@1</t>
+        </is>
+      </c>
       <c r="F9" s="12" t="inlineStr">
         <is>
-          <t>原表头：栽植成活率（按实际测算填写）；填 0-100 的百分数。 通过判断：≥85</t>
+          <t>原表头：栽植成活率（按实际测算填写）；填 0-100 的百分数。</t>
         </is>
       </c>
     </row>
@@ -14909,13 +14933,13 @@
       </c>
       <c r="D10" s="10" t="inlineStr">
         <is>
-          <t>数值(株→≥设计值)</t>
+          <t>数值(根→≥设计值)</t>
         </is>
       </c>
       <c r="E10" s="10" t="n"/>
       <c r="F10" s="12" t="inlineStr">
         <is>
-          <t>原表头：核实撑杆数量（1.数量达标2.数量不达标（填写实际数量）3.撑杆规格达标4.撑杆规格不达标）；原表把数量与规格合在一列，这里拆成「核实撑杆数量（数值）+ 撑杆规格（选项）」两行。 通过判断：≥设计值</t>
+          <t>原表头：核实撑杆数量（1.数量达标2.数量不达标（填写实际数量）3.撑杆规格达标4.撑杆规格不达标）；原表把数量与规格合在一列，这里拆成「核实撑杆数量（数值）+ 撑杆规格（选项）」两行。</t>
         </is>
       </c>
     </row>
@@ -14941,7 +14965,7 @@
       <c r="E11" s="10" t="n"/>
       <c r="F11" s="12" t="inlineStr">
         <is>
-          <t>原表头：核实撑杆数量（1.数量达标2.数量不达标（填写实际数量）3.撑杆规格达标4.撑杆规格不达标）；原表把数量与规格合在一列，这里拆成「核实撑杆数量（数值）+ 撑杆规格（选项）」两行。 选「不正确」须填 ≥2 汉字小备注。</t>
+          <t>原表头：核实撑杆数量（1.数量达标2.数量不达标（填写实际数量）3.撑杆规格达标4.撑杆规格不达标）；原表把数量与规格合在一列，这里拆成「核实撑杆数量（数值）+ 撑杆规格（选项）」两行。</t>
         </is>
       </c>
     </row>
@@ -14967,7 +14991,7 @@
       <c r="E12" s="10" t="n"/>
       <c r="F12" s="12" t="inlineStr">
         <is>
-          <t>原表头：核实覆膜数量（1.数量达标2.数量不达标（填写实际数量）3.覆膜质量达标4.覆膜质量不达标）；原表把数量与质量合在一列，这里拆成「核实覆膜数量（数值）+ 覆膜质量（选项）」两行。 通过判断：≥设计值</t>
+          <t>原表头：核实覆膜数量（1.数量达标2.数量不达标（填写实际数量）3.覆膜质量达标4.覆膜质量不达标）；原表把数量与质量合在一列，这里拆成「核实覆膜数量（数值）+ 覆膜质量（选项）」两行。</t>
         </is>
       </c>
     </row>
@@ -14993,7 +15017,7 @@
       <c r="E13" s="10" t="n"/>
       <c r="F13" s="12" t="inlineStr">
         <is>
-          <t>原表头：核实覆膜数量（1.数量达标2.数量不达标（填写实际数量）3.覆膜质量达标4.覆膜质量不达标）；原表把数量与质量合在一列，这里拆成「核实覆膜数量（数值）+ 覆膜质量（选项）」两行。 选「不正确」须填 ≥2 汉字小备注。</t>
+          <t>原表头：核实覆膜数量（1.数量达标2.数量不达标（填写实际数量）3.覆膜质量达标4.覆膜质量不达标）；原表把数量与质量合在一列，这里拆成「核实覆膜数量（数值）+ 覆膜质量（选项）」两行。</t>
         </is>
       </c>
     </row>
@@ -15012,10 +15036,14 @@
           <t>数值(株)</t>
         </is>
       </c>
-      <c r="E14" s="10" t="n"/>
+      <c r="E14" s="10" t="inlineStr">
+        <is>
+          <t>拍照:样地调查@1</t>
+        </is>
+      </c>
       <c r="F14" s="12" t="inlineStr">
         <is>
-          <t>原表头：样地调查成活株数；按数值填写，与设计值自动对照。</t>
+          <t>原表头：样地调查成活株数；按实测填写。</t>
         </is>
       </c>
     </row>
@@ -15037,7 +15065,7 @@
       <c r="E15" s="10" t="n"/>
       <c r="F15" s="12" t="inlineStr">
         <is>
-          <t>原表头：样地调查死亡株数；按数值填写，与设计值自动对照。</t>
+          <t>原表头：样地调查死亡株数；按实测填写。</t>
         </is>
       </c>
     </row>
@@ -15059,7 +15087,7 @@
       <c r="E16" s="10" t="n"/>
       <c r="F16" s="12" t="inlineStr">
         <is>
-          <t>原表头：样地调查成活率；自动计算，不手填。 通过判断：≥85</t>
+          <t>原表头：样地调查成活率；自动计算，不手填。</t>
         </is>
       </c>
     </row>
@@ -15271,14 +15299,14 @@
     <row r="2">
       <c r="A2" s="37" t="inlineStr">
         <is>
-          <t>版本 v2.7 ｜ 2026-10-28 ｜ 来源：tpl-人工造林-验收流程模板.xlsx</t>
+          <t>版本 v2.8 ｜ 2026-10-28 ｜ 来源：tpl-人工造林-验收流程模板.xlsx</t>
         </is>
       </c>
     </row>
     <row r="3" ht="30" customHeight="1">
       <c r="A3" s="37" t="inlineStr">
         <is>
-          <t>口径：模板由 tools/tpl_tool.py 从源表头自动解析生成；新增项目 / 流程只改源表或加 sheet，不改解析代码。</t>
+          <t>口径：模板由 tools/tpl/tpl_tool.py 从源表头自动解析生成；新增项目 / 流程只改源表或加 sheet，不改解析代码。</t>
         </is>
       </c>
     </row>
@@ -15481,7 +15509,7 @@
       </c>
       <c r="C25" s="37" t="inlineStr">
         <is>
-          <t>预留：上传附件 / 拍照。目前全部留空，后续按需填 拍照(现场;张数) 或 上传(照片,PDF)。</t>
+          <t>拍照:标签@张数 / 上传:标签@张数(图片≥A;PDF≥B)，半角冒号、@ 前为标签；拍照只存手机本机（C07/C09），上传件落服务器。当前：巡护行上传 3 份（图片≥1;PDF≥1）；面积 / 规格 / 质量 / 株数 / 成活率等关键环节拍照 1 张。</t>
         </is>
       </c>
     </row>
@@ -15493,7 +15521,7 @@
       </c>
       <c r="C26" s="37" t="inlineStr">
         <is>
-          <t>原始表头 + 归一 / 拆分说明，便于审计；「备注」行默认隐藏，不通过时展开。</t>
+          <t>原始表头 + 归一 / 拆分说明，便于审计；判定规则只写在控件 →规则 里，通用约定只在第六节，本列不重复。「备注」行默认隐藏，不通过时展开。</t>
         </is>
       </c>
     </row>
@@ -15539,7 +15567,7 @@
       <c r="D30" s="42" t="n"/>
       <c r="E30" s="41" t="inlineStr">
         <is>
-          <t>单选；第一项为默认；错误项可多个</t>
+          <t>单选；第一项为正向项「正确」，界面不预填、需显式选择；错误项可多个</t>
         </is>
       </c>
       <c r="F30" s="42" t="n"/>
@@ -15619,7 +15647,7 @@
       <c r="D34" s="42" t="n"/>
       <c r="E34" s="41" t="inlineStr">
         <is>
-          <t>非负数；与设计值自动对照</t>
+          <t>非负数；有设计值表头时自动对照</t>
         </is>
       </c>
       <c r="F34" s="42" t="n"/>
@@ -15753,13 +15781,13 @@
       <c r="B41" s="42" t="n"/>
       <c r="C41" s="41" t="inlineStr">
         <is>
-          <t>拍照(现场;1)</t>
+          <t>拍照:施工面积@1 / 上传:巡护资料@3(图片≥1;PDF≥1)</t>
         </is>
       </c>
       <c r="D41" s="42" t="n"/>
       <c r="E41" s="41" t="inlineStr">
         <is>
-          <t>填在「附件」列，本模板暂未使用</t>
+          <t>填在「附件」列；拍照=App 内实时拍摄、只存本机；上传=照片/PDF 落服务器</t>
         </is>
       </c>
       <c r="F41" s="42" t="n"/>
@@ -15809,7 +15837,7 @@
     <row r="50" ht="24" customHeight="1">
       <c r="A50" s="37" t="inlineStr">
         <is>
-          <t>1. 选项第一项固定为正向词「正确」，其后为错误项；错误项可以有多个。</t>
+          <t>1. 选项第一项固定为正向词「正确」，其后为错误项；错误项可以有多个。界面不预填，必须逐项显式选择；选项下方提示原表口径（如 已实施完成 / 未实施完成）。</t>
         </is>
       </c>
     </row>
@@ -15914,7 +15942,7 @@
     <row r="67" ht="30" customHeight="1">
       <c r="A67" s="37" t="inlineStr">
         <is>
-          <t>• 选项正向统一为「正确」，源表错误项保留；每个错误项须写 →备注≥2，选中时就地展开文本框。</t>
+          <t>• 选项正向统一为「正确」，源表错误项保留；每个错误项须写 →备注≥2，选中时就地展开文本框；原表说法作为界面提示展示。</t>
         </is>
       </c>
     </row>
